--- a/information_forms/012_open_peer_review_platform_registration--information_forms.xlsx
+++ b/information_forms/012_open_peer_review_platform_registration--information_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>first_name</t>
+          <t>submitting_institution</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>First name</t>
+          <t>Submitting Institution</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -704,154 +704,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>last_name</t>
+          <t>submitting_institution_address</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Last name</t>
+          <t>Submitting Institution Address</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>affiliation</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Affiliation</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>email</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Email</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>phone</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>role</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Role</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>submitting_institution</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Submitting Institution</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>submitting_institution_address</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Submitting Institution Address</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -868,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -939,57 +801,6 @@
         </is>
       </c>
       <c r="C4" t="inlineStr">
-        <is>
-          <t>Author</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>role_choices</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>editor</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Editor</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>role_choices</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>reviewer</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Reviewer</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>role_choices</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>author</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
         <is>
           <t>Author</t>
         </is>
